--- a/src/lib/template/achievements-template.xlsx
+++ b/src/lib/template/achievements-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\TOHO(Fajar)\KCF\MC Monitoring System\kcf-mc-monitoring\src\lib\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A51B529-D176-4635-B57D-6F27AB3DFFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD2B53-6120-4B9F-8079-7690537D682F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{370BB547-A0D3-4CB2-B344-9D3804543135}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{370BB547-A0D3-4CB2-B344-9D3804543135}"/>
   </bookViews>
   <sheets>
     <sheet name="OPERATOR" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="135" r:id="rId5"/>
+    <pivotCache cacheId="48" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="47">
   <si>
     <t>DATE</t>
   </si>
@@ -184,11 +184,17 @@
   <si>
     <t>DANDORI.</t>
   </si>
+  <si>
+    <t>(All)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -287,7 +293,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -323,24 +329,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="60% - Accent2" xfId="1" builtinId="36"/>
     <cellStyle name="60% - Accent6" xfId="2" builtinId="52"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="18">
     <dxf>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -618,7 +641,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable17</c:name>
-    <c:fmtId val="10"/>
+    <c:fmtId val="40"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -720,70 +743,11 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="percentStacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -833,7 +797,7 @@
             <c:numRef>
               <c:f>'RATE FORGING'!$E$2</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -841,7 +805,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3DA9-4ED5-9977-122987A01E8F}"/>
+              <c16:uniqueId val="{00000000-AFD4-49AB-98E1-C2D7D0186AD9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -854,11 +818,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="150133440"/>
-        <c:axId val="2011588912"/>
+        <c:axId val="714793359"/>
+        <c:axId val="719723791"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="150133440"/>
+        <c:axId val="714793359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -901,7 +865,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2011588912"/>
+        <c:crossAx val="719723791"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -909,10 +873,9 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2011588912"/>
+        <c:axId val="719723791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="0.5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -930,7 +893,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -961,10 +924,9 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="150133440"/>
+        <c:crossAx val="714793359"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="0.1"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1006,7 +968,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -1079,8 +1041,412 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
+    <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable24</c:name>
+    <c:fmtId val="42"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:strRef>
+          <c:f>'RATE FORGING'!$R$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>OPERATING RATE SF-100-1 (TARGET 85%)</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$R$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$R$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="2"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Jun</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Sep</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$R$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DFDC-4932-9F18-B2A0EE1EE73F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="714797071"/>
+        <c:axId val="719646511"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="714797071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="719646511"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="719646511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="714797071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
     <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable20</c:name>
-    <c:fmtId val="17"/>
+    <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -1182,70 +1548,11 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="percentStacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1295,7 +1602,7 @@
             <c:numRef>
               <c:f>'RATE FORGING'!$E$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -1303,7 +1610,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-43E7-434B-AEFB-A99773DA08A8}"/>
+              <c16:uniqueId val="{00000000-134C-4BBE-8F1D-5E1663BBD29F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1316,11 +1623,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="134345808"/>
-        <c:axId val="1998675376"/>
+        <c:axId val="694761487"/>
+        <c:axId val="719687791"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="134345808"/>
+        <c:axId val="694761487"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1363,7 +1670,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1998675376"/>
+        <c:crossAx val="719687791"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1371,7 +1678,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1998675376"/>
+        <c:axId val="719687791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1391,7 +1698,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1422,7 +1729,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="134345808"/>
+        <c:crossAx val="694761487"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1466,7 +1773,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -1525,7 +1832,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1540,7 +1847,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable21</c:name>
-    <c:fmtId val="17"/>
+    <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -1642,70 +1949,11 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="percentStacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1755,7 +2003,7 @@
             <c:numRef>
               <c:f>'RATE FORGING'!$E$46</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -1763,7 +2011,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-73C1-493E-80E7-3F1F6E917DAA}"/>
+              <c16:uniqueId val="{00000000-267C-423F-8A92-EEA03A1CACF8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1776,11 +2024,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="284249648"/>
-        <c:axId val="1998677296"/>
+        <c:axId val="694731791"/>
+        <c:axId val="719629711"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="284249648"/>
+        <c:axId val="694731791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1823,7 +2071,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1998677296"/>
+        <c:crossAx val="719629711"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1831,7 +2079,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1998677296"/>
+        <c:axId val="719629711"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1851,7 +2099,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1882,7 +2130,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="284249648"/>
+        <c:crossAx val="694731791"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1926,7 +2174,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -1985,7 +2233,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2000,7 +2248,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable25</c:name>
-    <c:fmtId val="19"/>
+    <c:fmtId val="21"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -2102,67 +2350,11 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="percentStacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -2212,7 +2404,7 @@
             <c:numRef>
               <c:f>'RATE FORGING'!$E$67</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -2220,7 +2412,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DBE7-43FD-9240-0FF83871C56D}"/>
+              <c16:uniqueId val="{00000000-058B-4F9D-9220-D8007F66E039}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2233,11 +2425,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="284279808"/>
-        <c:axId val="1998654256"/>
+        <c:axId val="694689567"/>
+        <c:axId val="719681551"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="284279808"/>
+        <c:axId val="694689567"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2280,7 +2472,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1998654256"/>
+        <c:crossAx val="719681551"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2288,7 +2480,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1998654256"/>
+        <c:axId val="719681551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2308,7 +2500,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2339,7 +2531,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="284279808"/>
+        <c:crossAx val="694689567"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2383,470 +2575,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable24</c:name>
-    <c:fmtId val="40"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:strRef>
-          <c:f>'RATE FORGING'!$R$2</c:f>
-          <c:strCache>
-            <c:ptCount val="1"/>
-            <c:pt idx="0">
-              <c:v>OPERATING RATE SF-100-1 (TARGET 85%)</c:v>
-            </c:pt>
-          </c:strCache>
-        </c:strRef>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="percentStacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$R$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$R$2</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="2"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Jun</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Sep</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$R$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-952E-4925-96A8-5875C8951C1E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="2142564400"/>
-        <c:axId val="1998610576"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="2142564400"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1998610576"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1998610576"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2142564400"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -2920,7 +2649,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable23</c:name>
-    <c:fmtId val="17"/>
+    <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -3022,70 +2751,11 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="percentStacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -3138,7 +2808,7 @@
             <c:numRef>
               <c:f>'RATE FORGING'!$R$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
@@ -3146,7 +2816,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1327-463E-8795-8CE12FDDEB65}"/>
+              <c16:uniqueId val="{00000000-8639-4D4F-843F-4A5A69F26024}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3159,11 +2829,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="702183152"/>
-        <c:axId val="1998683056"/>
+        <c:axId val="714800783"/>
+        <c:axId val="719711311"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="702183152"/>
+        <c:axId val="714800783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3206,7 +2876,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1998683056"/>
+        <c:crossAx val="719711311"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3214,7 +2884,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1998683056"/>
+        <c:axId val="719711311"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3234,7 +2904,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3265,7 +2935,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="702183152"/>
+        <c:crossAx val="714800783"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3309,7 +2979,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -3383,7 +3053,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable22</c:name>
-    <c:fmtId val="17"/>
+    <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -3485,70 +3155,11 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="percentStacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -3601,7 +3212,7 @@
             <c:numRef>
               <c:f>'RATE FORGING'!$R$46</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
@@ -3609,7 +3220,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9C07-4F7B-952D-619C66D459C0}"/>
+              <c16:uniqueId val="{00000000-6C24-4CFC-822E-7EF86C7F1038}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3622,11 +3233,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="702314928"/>
-        <c:axId val="1998672496"/>
+        <c:axId val="714769695"/>
+        <c:axId val="719634031"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="702314928"/>
+        <c:axId val="714769695"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3669,7 +3280,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1998672496"/>
+        <c:crossAx val="719634031"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3677,7 +3288,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1998672496"/>
+        <c:axId val="719634031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3697,7 +3308,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3728,7 +3339,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="702314928"/>
+        <c:crossAx val="714769695"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3772,7 +3383,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -3846,7 +3457,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable26</c:name>
-    <c:fmtId val="19"/>
+    <c:fmtId val="21"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -3948,67 +3559,11 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="percentStacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -4058,7 +3613,7 @@
             <c:numRef>
               <c:f>'RATE FORGING'!$R$67</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -4066,7 +3621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CF94-487D-838B-4E9BE701CB89}"/>
+              <c16:uniqueId val="{00000000-1F52-4F29-A13E-AC893765C0AE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4079,11 +3634,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="702278736"/>
-        <c:axId val="1998704656"/>
+        <c:axId val="164307023"/>
+        <c:axId val="719705071"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="702278736"/>
+        <c:axId val="164307023"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4126,7 +3681,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1998704656"/>
+        <c:crossAx val="719705071"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4134,7 +3689,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1998704656"/>
+        <c:axId val="719705071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4154,7 +3709,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4185,7 +3740,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="702278736"/>
+        <c:crossAx val="164307023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4229,7 +3784,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -4302,21 +3857,39 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable27</c:name>
-    <c:fmtId val="21"/>
+    <c:name>[achievements-template.xlsx]TOTAL RATE!PivotTable1</c:name>
+    <c:fmtId val="6"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
-        <c:strRef>
-          <c:f>'RATE FORGING'!$E$89</c:f>
-          <c:strCache>
-            <c:ptCount val="1"/>
-            <c:pt idx="0">
-              <c:v>OPERATING RATE SF-50-1 (TARGET 85%)</c:v>
-            </c:pt>
-          </c:strCache>
-        </c:strRef>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>TOTAL</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> RATE</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
@@ -4405,74 +3978,18 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="percentStacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'RATE FORGING'!$E$89</c:f>
+              <c:f>'TOTAL RATE'!$D$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4495,11 +4012,44 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$E$89</c:f>
+              <c:f>'TOTAL RATE'!$C$8:$C$21</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="12"/>
                 <c:lvl>
                   <c:pt idx="0">
+                    <c:v>Jan</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Feb</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Mar</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Apr</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>May</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jun</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Sep</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Oct</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Nov</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
                     <c:v>Dec</c:v>
                   </c:pt>
                 </c:lvl>
@@ -4513,17 +4063,17 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'RATE FORGING'!$E$89</c:f>
+              <c:f>'TOTAL RATE'!$D$8:$D$21</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="12"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2BAB-4950-A7CC-656FB628983F}"/>
+              <c16:uniqueId val="{00000000-E2C9-4CB6-A41C-60A2012F1C2F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4536,11 +4086,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="702186400"/>
-        <c:axId val="1998668656"/>
+        <c:axId val="597353679"/>
+        <c:axId val="719682031"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="702186400"/>
+        <c:axId val="597353679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4583,7 +4133,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1998668656"/>
+        <c:crossAx val="719682031"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4591,7 +4141,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1998668656"/>
+        <c:axId val="719682031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4611,7 +4161,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4642,7 +4192,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="702186400"/>
+        <c:crossAx val="597353679"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4686,7 +4236,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
@@ -9754,22 +9304,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>223837</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>528637</xdr:colOff>
+      <xdr:colOff>409575</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36A9B642-A746-BAB2-3C1F-81320BFCAB16}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD4EED71-A9EF-2658-6BE7-BE55235C0EDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9789,23 +9339,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="10" name="Chart 9">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA96A717-CD7D-A89D-049D-F1E0AE204B4A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D789AAAA-3049-2322-120A-5FEDC8037FE2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9826,22 +9376,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:colOff>33337</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:colOff>338137</xdr:colOff>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="11" name="Chart 10">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD59CCB0-3D9F-47CE-32BD-67B987B23A2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF764254-538F-6DAD-3FCC-BF14D4EA746D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9862,22 +9412,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>328612</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="12" name="Chart 11">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80BA529F-2DA8-9FC7-84DB-03A0C68D2AF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E90D701-D890-8DCC-7D7F-F1457640AAF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9897,23 +9447,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>33337</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>338137</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="13" name="Chart 12">
+        <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99A89110-500D-938B-E915-550166B9787F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2954E4E2-7828-3A41-B4BF-F10CE4A3B98B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9934,22 +9484,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
+      <xdr:colOff>176212</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
+      <xdr:colOff>681037</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="14" name="Chart 13">
+        <xdr:cNvPr id="8" name="Chart 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3F0837E-C826-05EE-538D-83A2043BFFD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F23D371-6344-F449-086D-FBD83395E283}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9970,22 +9520,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:colOff>214312</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>704850</xdr:colOff>
+      <xdr:colOff>719137</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="15" name="Chart 14">
+        <xdr:cNvPr id="9" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60610E88-0CB6-151A-1E31-FEB2BD80184A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC43CF57-4ACF-C8E2-8170-2282CF13181B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10006,22 +9556,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:colOff>214312</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
+      <xdr:colOff>719137</xdr:colOff>
       <xdr:row>80</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="16" name="Chart 15">
+        <xdr:cNvPr id="18" name="Chart 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1E9C2A4-9E15-B4EE-6B86-EF31F048EA71}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EEEEEB6-F9D1-1714-E20B-FAF02E556D29}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10039,25 +9589,30 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>128587</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>433387</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="17" name="Chart 16">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5A4733C-A08A-AE12-8F9A-4CEBB2D2C641}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DDE686E-7737-73FE-C197-244D05D5FC1D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10069,7 +9624,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10349,7 +9904,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2768C1A7-CF4D-4B1A-9488-2D606A57C0D6}" name="PivotTable29" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2768C1A7-CF4D-4B1A-9488-2D606A57C0D6}" name="PivotTable29" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B9:O12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -10459,8 +10014,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1099930-AA0D-42B1-B26F-6D33ECEE56A5}" name="PivotTable21" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
-  <location ref="B48:C51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CDF4683-225E-491F-BC53-BACA1AD4F4FB}" name="PivotTable23" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="O27:P31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -10500,7 +10055,13 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -10515,12 +10076,15 @@
     <field x="1"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
     <i r="1">
-      <x v="1"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
     </i>
     <i t="grand">
       <x/>
@@ -10529,147 +10093,12 @@
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="7" hier="-1"/>
+  <pageFields count="2">
+    <pageField fld="3" item="4" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B55F4480-DCD5-4360-899D-5EEB6809EDFC}" name="PivotTable26" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="O69:P72" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
   </dataFields>
   <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
@@ -10739,9 +10168,200 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A01F2CE9-B7B1-443F-AC32-A00886791260}" name="PivotTable12" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="CS4:CU7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52385311-543D-48DA-9DB8-077801849FE9}" name="PivotTable24" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="42">
-  <location ref="O4:P8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A90CBD1C-EB98-462C-B899-A137F77093F8}" name="PivotTable13" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="CC4:CF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52385311-543D-48DA-9DB8-077801849FE9}" name="PivotTable24" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
+  <location ref="O5:P9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -10781,7 +10401,13 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -10813,13 +10439,14 @@
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="1">
+  <pageFields count="2">
     <pageField fld="3" item="1" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
   </dataFields>
-  <chartFormats count="9">
+  <chartFormats count="10">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -10901,6 +10528,15 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="42" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -10914,9 +10550,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221D5A86-0FAF-4D4D-9C44-7BE90E19394D}" name="PivotTable9" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="AT4:AW7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04461318-0B3E-47A8-BB7B-19F4A3469DF7}" name="PivotTable8" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="AD4:AF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
       <items count="13">
@@ -10982,19 +10618,16 @@
   <colFields count="1">
     <field x="0"/>
   </colFields>
-  <colItems count="3">
+  <colItems count="2">
     <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
+      <x v="11"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="3" item="1" hier="-1"/>
+    <pageField fld="3" item="0" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
@@ -11011,147 +10644,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E75A289-3383-4298-8FCC-8F5B4061FFF8}" name="PivotTable22" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
-  <location ref="O48:P52" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6D0FF5-F6F2-4E98-A793-3425B75F1FFE}" name="PivotTable15" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6D0FF5-F6F2-4E98-A793-3425B75F1FFE}" name="PivotTable15" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="EM4:EO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -11245,8 +10739,102 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F2800DD-182C-4C60-A59A-C1128AAB24B1}" name="PivotTable17" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="40">
-  <location ref="B4:C7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A17830ED-8927-4755-8501-7DFC778792DA}" name="PivotTable11" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="DH4:DJ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B55F4480-DCD5-4360-899D-5EEB6809EDFC}" name="PivotTable26" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="O70:P73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -11286,7 +10874,13 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -11306,7 +10900,7 @@
       <x/>
     </i>
     <i r="1">
-      <x v="9"/>
+      <x v="10"/>
     </i>
     <i t="grand">
       <x/>
@@ -11315,671 +10909,12 @@
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="2" hier="-1"/>
+  <pageFields count="2">
+    <pageField fld="3" item="8" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="38" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A90CBD1C-EB98-462C-B899-A137F77093F8}" name="PivotTable13" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="CC4:CF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A01F2CE9-B7B1-443F-AC32-A00886791260}" name="PivotTable12" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="CS4:CU7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04461318-0B3E-47A8-BB7B-19F4A3469DF7}" name="PivotTable8" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="AD4:AF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="0" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBEFD717-55D2-4077-BD74-B3665F7BCED5}" name="PivotTable14" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="DX4:DZ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C678E28A-B4DB-4C7B-9C04-D16A9B79A051}" name="PivotTable20" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
-  <location ref="B26:C29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E9197E-66A0-4212-8D82-1C76DDF3FEE7}" name="PivotTable27" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="B91:C94" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="5" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
   </dataFields>
   <chartFormats count="7">
     <chartFormat chart="0" format="0" series="1">
@@ -12058,9 +10993,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A17830ED-8927-4755-8501-7DFC778792DA}" name="PivotTable11" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="DH4:DJ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{078CD331-B6DD-42D6-A2EA-38A1DC462D3C}" name="PivotTable10" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="BL4:BO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
       <items count="13">
@@ -12126,16 +11061,19 @@
   <colFields count="1">
     <field x="0"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="3">
     <i>
-      <x/>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="7"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="3" item="6" hier="-1"/>
+    <pageField fld="3" item="2" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
@@ -12152,9 +11090,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32494390-7516-4808-9564-94C6298A0B64}" name="PivotTable25" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="B69:C72" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C678E28A-B4DB-4C7B-9C04-D16A9B79A051}" name="PivotTable20" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="B27:C30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -12194,7 +11132,13 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -12214,7 +11158,7 @@
       <x/>
     </i>
     <i r="1">
-      <x v="2"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -12223,11 +11167,12 @@
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="0" hier="-1"/>
+  <pageFields count="2">
+    <pageField fld="3" item="6" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
   </dataFields>
   <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
@@ -12297,200 +11242,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983F6769-FF4F-45FA-A00D-3D6DA862D39D}" name="PivotTable28" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="FB4:FD7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="5" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{078CD331-B6DD-42D6-A2EA-38A1DC462D3C}" name="PivotTable10" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="BL4:BO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="2" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CDF4683-225E-491F-BC53-BACA1AD4F4FB}" name="PivotTable23" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
-  <location ref="O26:P30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1099930-AA0D-42B1-B26F-6D33ECEE56A5}" name="PivotTable21" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="B50:C53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -12530,7 +11284,13 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -12545,15 +11305,12 @@
     <field x="1"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="3">
     <i>
       <x/>
     </i>
     <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -12562,13 +11319,14 @@
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="4" hier="-1"/>
+  <pageFields count="2">
+    <pageField fld="3" item="7" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0"/>
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -12614,6 +11372,1133 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3913DF35-F900-4B9E-A461-7854FE3E9E8A}" name="PivotTable1" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="C7:D21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="count" baseField="0" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="2">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221D5A86-0FAF-4D4D-9C44-7BE90E19394D}" name="PivotTable9" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="AT4:AW7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983F6769-FF4F-45FA-A00D-3D6DA862D39D}" name="PivotTable28" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="FB4:FD7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="5" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBEFD717-55D2-4077-BD74-B3665F7BCED5}" name="PivotTable14" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="DX4:DZ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F2800DD-182C-4C60-A59A-C1128AAB24B1}" name="PivotTable17" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="42">
+  <location ref="B5:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="2" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="38" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="40" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E75A289-3383-4298-8FCC-8F5B4061FFF8}" name="PivotTable22" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="O49:P53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E9197E-66A0-4212-8D82-1C76DDF3FEE7}" name="PivotTable27" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="B92:C95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="5" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32494390-7516-4808-9564-94C6298A0B64}" name="PivotTable25" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="B70:C73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="0" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="4">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="7">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -12631,23 +12516,25 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8771DFAE-D88A-41F3-BFC3-CA435140B509}" name="Table4" displayName="Table4" ref="C2:O14" totalsRowShown="0">
   <autoFilter ref="C2:O14" xr:uid="{8771DFAE-D88A-41F3-BFC3-CA435140B509}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{AA0F4A8A-C024-4FC6-9787-B30556B07C4D}" name="MONTH" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{AA0F4A8A-C024-4FC6-9787-B30556B07C4D}" name="MONTH" dataDxfId="17">
       <calculatedColumnFormula>TEXT(E3, "mmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A8A40FED-5AE6-4F3B-A482-2DC859CBECE8}" name="YEAR" dataDxfId="11">
+    <tableColumn id="12" xr3:uid="{A8A40FED-5AE6-4F3B-A482-2DC859CBECE8}" name="YEAR" dataDxfId="16">
       <calculatedColumnFormula>TEXT(Table4[[#This Row],[DATE]], "yyyy")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53BAB48D-3DEC-4471-BE46-1798702D2303}" name="DATE" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{66B8BA99-4483-49FA-917F-E23A0082F7AE}" name="MACHINE" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{807EF872-0464-40F2-9E8E-2E197E4E4F0F}" name="ITEM NO" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{62AABD23-67B8-4240-81EE-9690684F857B}" name="ITEM NAME" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{ECC4F505-5088-4655-955E-FFCF79127D17}" name="SPEED (M)" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{88E606BF-77D9-43BC-A245-5060F9FFB2DC}" name="SPEED (H)" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{559CFE2C-A093-4C69-8644-EA4041670421}" name="OPERATOR" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{34427C21-CCE4-495D-849E-C8CE3AAF98F2}" name="DANDORI T." dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{D5BBBED8-248D-4454-BE79-04A39D6BF301}" name="RUNNING T. " dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{B0EFB25E-6FC0-43A9-9EF6-C8CD305D25B8}" name="PRODUCT QTY" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{D9DBE70D-60F1-4AB6-B94B-1334C66C922A}" name="OPERATING RATE" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{53BAB48D-3DEC-4471-BE46-1798702D2303}" name="DATE" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{66B8BA99-4483-49FA-917F-E23A0082F7AE}" name="MACHINE" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{807EF872-0464-40F2-9E8E-2E197E4E4F0F}" name="ITEM NO" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{62AABD23-67B8-4240-81EE-9690684F857B}" name="ITEM NAME" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{ECC4F505-5088-4655-955E-FFCF79127D17}" name="SPEED (M)" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{88E606BF-77D9-43BC-A245-5060F9FFB2DC}" name="SPEED (H)" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{559CFE2C-A093-4C69-8644-EA4041670421}" name="OPERATOR" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{34427C21-CCE4-495D-849E-C8CE3AAF98F2}" name="DANDORI T." dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{D5BBBED8-248D-4454-BE79-04A39D6BF301}" name="RUNNING T. " dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{B0EFB25E-6FC0-43A9-9EF6-C8CD305D25B8}" name="PRODUCT QTY" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{D9DBE70D-60F1-4AB6-B94B-1334C66C922A}" name="OPERATING RATE" dataDxfId="5">
+      <calculatedColumnFormula>IF(Table4[[#This Row],[PRODUCT QTY]] = "", "", Table4[[#This Row],[PRODUCT QTY]]/(Table4[[#This Row],[RUNNING T. ]]*Table4[[#This Row],[SPEED (M)]]))</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12988,33 +12875,33 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -13072,37 +12959,11 @@
       <c r="B11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13117,18 +12978,18 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:FD94"/>
+  <dimension ref="B1:FD95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="38.5703125" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.85546875" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="1.28515625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="37" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -13169,14 +13030,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:160" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
     </row>
     <row r="2" spans="2:160" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
@@ -13254,19 +13115,21 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="2:160" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="4" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" t="s">
-        <v>40</v>
-      </c>
       <c r="AD4" s="10" t="s">
         <v>20</v>
       </c>
@@ -13323,11 +13186,17 @@
       </c>
     </row>
     <row r="5" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" t="s">
+        <v>40</v>
       </c>
       <c r="AD5" s="10" t="s">
         <v>12</v>
@@ -13421,12 +13290,14 @@
       </c>
     </row>
     <row r="6" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" s="14" t="s">
-        <v>36</v>
-      </c>
+      <c r="B6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="O6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="19"/>
       <c r="AD6" s="11" t="s">
         <v>13</v>
       </c>
@@ -13456,12 +13327,14 @@
       </c>
     </row>
     <row r="7" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="B7" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="B7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="19"/>
       <c r="O7" s="14" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="P7" s="19"/>
       <c r="AD7" s="11" t="s">
         <v>14</v>
       </c>
@@ -13491,9 +13364,20 @@
       </c>
     </row>
     <row r="8" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="O8" s="11" t="s">
+      <c r="B8" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="C8" s="19"/>
+      <c r="O8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="19"/>
+    </row>
+    <row r="9" spans="2:160" x14ac:dyDescent="0.25">
+      <c r="O9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P9" s="19"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
@@ -13517,58 +13401,73 @@
         <v>OPERATING RATE SF-200-2 (TARGET 85%)</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" t="s">
-        <v>40</v>
-      </c>
-      <c r="O26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="P26" t="s">
-        <v>40</v>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P25" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="O27" s="11" t="s">
-        <v>43</v>
+      <c r="B27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="P27" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="O28" s="14" t="s">
-        <v>37</v>
-      </c>
+      <c r="B28" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="O28" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P28" s="19"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="B29" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="19"/>
       <c r="O29" s="14" t="s">
-        <v>30</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="P29" s="19"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="O30" s="11" t="s">
+      <c r="B30" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="C30" s="19"/>
+      <c r="O30" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="P30" s="19"/>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P31" s="19"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>27</v>
-      </c>
       <c r="E46" t="str">
-        <f>"OPERATING RATE "&amp;C46&amp;" (TARGET 85%)"</f>
+        <f>"OPERATING RATE "&amp;C47&amp;" (TARGET 85%)"</f>
         <v>OPERATING RATE SF-50-3 (TARGET 85%)</v>
       </c>
       <c r="O46" s="10" t="s">
@@ -13582,48 +13481,77 @@
         <v>OPERATING RATE SF-200-1 (TARGET 85%)</v>
       </c>
     </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B47" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P47" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O49" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C48" t="s">
+      <c r="P49" t="s">
         <v>40</v>
       </c>
-      <c r="O48" s="10" t="s">
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B50" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="P48" t="s">
+      <c r="C50" t="s">
         <v>40</v>
       </c>
+      <c r="O50" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P50" s="19"/>
     </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B49" s="11" t="s">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B51" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="O49" s="11" t="s">
-        <v>43</v>
-      </c>
+      <c r="C51" s="19"/>
+      <c r="O51" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" s="19"/>
     </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="14" t="s">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B52" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="O50" s="14" t="s">
-        <v>38</v>
-      </c>
+      <c r="C52" s="19"/>
+      <c r="O52" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="P52" s="19"/>
     </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B51" s="11" t="s">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B53" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="O51" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="O52" s="11" t="s">
+      <c r="C53" s="19"/>
+      <c r="O53" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="P53" s="19"/>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B67" s="10" t="s">
@@ -13647,49 +13575,63 @@
         <v>OPERATING RATE SF-80 (TARGET 85%)</v>
       </c>
     </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B69" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" t="s">
-        <v>40</v>
-      </c>
-      <c r="O69" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="P69" t="s">
-        <v>40</v>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B68" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>46</v>
+      </c>
+      <c r="O68" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P68" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B70" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C70" s="18"/>
-      <c r="O70" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="P70" s="18"/>
+      <c r="B70" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" t="s">
+        <v>40</v>
+      </c>
+      <c r="O70" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="P70" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B71" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C71" s="18"/>
-      <c r="O71" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="P71" s="18"/>
+      <c r="B71" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71" s="19"/>
+      <c r="O71" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P71" s="19"/>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C72" s="19"/>
+      <c r="O72" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="P72" s="19"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B73" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C72" s="18"/>
-      <c r="O72" s="11" t="s">
+      <c r="C73" s="19"/>
+      <c r="O73" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P72" s="18"/>
+      <c r="P73" s="19"/>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" s="10" t="s">
@@ -13703,31 +13645,39 @@
         <v>OPERATING RATE SF-50-1 (TARGET 85%)</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B91" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C91" t="s">
-        <v>40</v>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C92" s="18"/>
+      <c r="B92" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C93" s="18"/>
+      <c r="B93" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C93" s="19"/>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="19"/>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C94" s="18"/>
+      <c r="C95" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13740,10 +13690,117 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C17C2FC-B423-40AA-AB87-06D0390D0599}">
-  <dimension ref="A1"/>
+  <dimension ref="C5:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="19"/>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="19"/>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="19"/>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="19"/>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="19"/>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="19"/>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="19"/>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="19"/>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="19"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -13760,8 +13817,8 @@
     <col min="4" max="4" width="9.85546875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.7109375" customWidth="1"/>
+    <col min="7" max="7" width="36.7109375" customWidth="1"/>
+    <col min="8" max="8" width="45.140625" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
     <col min="10" max="11" width="14.42578125" customWidth="1"/>
     <col min="12" max="12" width="14.140625" customWidth="1"/>
@@ -13771,11 +13828,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
@@ -13837,13 +13894,11 @@
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="O3" s="18"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="13"/>
@@ -13869,7 +13924,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="O4" s="18"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
@@ -13895,7 +13950,7 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="18"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
@@ -13921,7 +13976,7 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="O6" s="18"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="13"/>
@@ -13947,7 +14002,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="O7" s="18"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
@@ -13973,7 +14028,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="O8" s="18"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="13"/>
@@ -13999,7 +14054,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+      <c r="O9" s="18"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="13"/>
@@ -14025,7 +14080,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="13"/>
@@ -14051,7 +14106,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="O11" s="18"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="13"/>
@@ -14077,7 +14132,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="O12" s="18"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="13"/>
@@ -14103,7 +14158,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
+      <c r="O13" s="18"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="13"/>
@@ -14129,7 +14184,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="O14" s="18"/>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E17" t="s">

--- a/src/lib/template/achievements-template.xlsx
+++ b/src/lib/template/achievements-template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\TOHO(Fajar)\KCF\MC Monitoring System\kcf-mc-monitoring\src\lib\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD2B53-6120-4B9F-8079-7690537D682F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FF9F06-1F61-46D9-8A77-85892EB9301A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{370BB547-A0D3-4CB2-B344-9D3804543135}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{370BB547-A0D3-4CB2-B344-9D3804543135}"/>
   </bookViews>
   <sheets>
     <sheet name="OPERATOR" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="48" r:id="rId5"/>
+    <pivotCache cacheId="12" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="51">
   <si>
     <t>DATE</t>
   </si>
@@ -182,10 +182,22 @@
     <t xml:space="preserve">DANDORI </t>
   </si>
   <si>
-    <t>DANDORI.</t>
+    <t>(All)</t>
   </si>
   <si>
-    <t>(All)</t>
+    <t>DANDORI T AVG.</t>
+  </si>
+  <si>
+    <t>AVG</t>
+  </si>
+  <si>
+    <t>PRODUKTIFITAS PRODUKSI</t>
+  </si>
+  <si>
+    <t>TARGET 85 %</t>
+  </si>
+  <si>
+    <t>TARGET 85%</t>
   </si>
 </sst>
 </file>
@@ -193,9 +205,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +231,13 @@
     </font>
     <font>
       <sz val="36"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -293,7 +312,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -329,38 +348,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="60% - Accent2" xfId="1" builtinId="36"/>
     <cellStyle name="60% - Accent6" xfId="2" builtinId="52"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="41">
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
@@ -732,6 +824,188 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -758,7 +1032,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -775,6 +1049,64 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'RATE FORGING'!$E$2</c:f>
@@ -799,6 +1131,9 @@
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -809,9 +1144,76 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$E$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Oct</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-8205-4FE0-84FA-47646E5DFA68}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -925,6 +1327,687 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="714793359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[achievements-template.xlsx]TOTAL RATE!PivotTable1</c:name>
+    <c:fmtId val="6"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>TOTAL PRESENTASE PRODUKSIFITAS </a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>(TARGET 85 %)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TOTAL RATE'!$D$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RATE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'TOTAL RATE'!$C$8:$C$21</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Jan</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Feb</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Mar</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Apr</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>May</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jun</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Sep</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Oct</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Nov</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Dec</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TOTAL RATE'!$D$8:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E2C9-4CB6-A41C-60A2012F1C2F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TOTAL RATE'!$E$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85 %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'TOTAL RATE'!$C$8:$C$21</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Jan</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Feb</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Mar</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Apr</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>May</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Jun</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Sep</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Oct</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Nov</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Dec</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TOTAL RATE'!$E$8:$E$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-311B-4504-96A1-F56A813C4347}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="597353679"/>
+        <c:axId val="719682031"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="597353679"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="719682031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="719682031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="597353679"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1133,6 +2216,121 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1159,7 +2357,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1176,6 +2374,64 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'RATE FORGING'!$R$2</c:f>
@@ -1203,6 +2459,12 @@
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1213,9 +2475,82 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$R$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$R$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="2"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Jun</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Sep</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$R$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7474-4845-8AE0-346C2BA91012}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1537,6 +2872,131 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1563,7 +3023,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1580,6 +3040,64 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'RATE FORGING'!$E$24</c:f>
@@ -1604,6 +3122,9 @@
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1614,9 +3135,76 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$E$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$E$24</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Jan</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$E$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C8E9-4475-9990-8ECB2A2AA79C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1938,6 +3526,131 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1964,7 +3677,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1981,6 +3694,64 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'RATE FORGING'!$E$46</c:f>
@@ -2005,6 +3776,9 @@
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2015,9 +3789,76 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$E$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$E$46</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Feb</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$E$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-ABBE-44CF-8CC9-12380C06D757}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -2339,6 +4180,131 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2365,7 +4331,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2382,6 +4348,64 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'RATE FORGING'!$E$67</c:f>
@@ -2406,6 +4430,9 @@
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2416,9 +4443,76 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$E$67</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$E$67</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Mar</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$E$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A0F7-418E-9FC0-27D7FC2807A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -2740,6 +4834,131 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2766,7 +4985,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2783,6 +5002,64 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'RATE FORGING'!$R$24</c:f>
@@ -2810,6 +5087,12 @@
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2820,9 +5103,82 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$R$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$R$24</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="2"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>May</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$R$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FE4A-4607-9E05-654003A53AB6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -3144,6 +5500,131 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3170,7 +5651,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3187,6 +5668,64 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'RATE FORGING'!$R$46</c:f>
@@ -3214,6 +5753,12 @@
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3224,9 +5769,82 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$R$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$R$46</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="2"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Apr</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$R$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-46CB-4242-A579-73626F7AF683}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -3548,6 +6166,131 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3574,7 +6317,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3591,6 +6334,64 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>'RATE FORGING'!$R$67</c:f>
@@ -3615,6 +6416,9 @@
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3625,9 +6429,76 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$R$67</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$R$67</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Nov</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$R$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7FB7-412B-ADC6-7C89B79BE3CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -3857,39 +6728,21 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[achievements-template.xlsx]TOTAL RATE!PivotTable1</c:name>
-    <c:fmtId val="6"/>
+    <c:name>[achievements-template.xlsx]RATE FORGING!PivotTable27</c:name>
+    <c:fmtId val="23"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>TOTAL</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> RATE</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>'RATE FORGING'!$E$89</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>OPERATING RATE SF-50-1 (TARGET 85%)</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
@@ -3967,6 +6820,131 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3989,11 +6967,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'TOTAL RATE'!$D$7</c:f>
+              <c:f>'RATE FORGING'!$E$89</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>RATE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4010,46 +6988,71 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'TOTAL RATE'!$C$8:$C$21</c:f>
+              <c:f>'RATE FORGING'!$E$89</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="1"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Jan</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Feb</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Mar</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Apr</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>May</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Jun</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Jul</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Aug</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Sep</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>Oct</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Nov</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
                     <c:v>Dec</c:v>
                   </c:pt>
                 </c:lvl>
@@ -4063,34 +7066,104 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TOTAL RATE'!$D$8:$D$21</c:f>
+              <c:f>'RATE FORGING'!$E$89</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E2C9-4CB6-A41C-60A2012F1C2F}"/>
+              <c16:uniqueId val="{00000000-CA59-475C-8CEB-7C9FB64A9A1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'RATE FORGING'!$E$89</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TARGET 85%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'RATE FORGING'!$E$89</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Dec</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RATE FORGING'!$E$89</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-668A-446B-AD34-F91B3FF10546}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="597353679"/>
-        <c:axId val="719682031"/>
+        <c:axId val="133776416"/>
+        <c:axId val="121995600"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="597353679"/>
+        <c:axId val="133776416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4133,7 +7206,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="719682031"/>
+        <c:crossAx val="121995600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4141,7 +7214,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="719682031"/>
+        <c:axId val="121995600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4192,7 +7265,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="597353679"/>
+        <c:crossAx val="133776416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4296,6 +7369,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5171,6 +8284,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -9520,15 +13149,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>214312</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>185737</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>719137</xdr:colOff>
+      <xdr:colOff>690562</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9589,6 +13218,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0119F0EE-FA57-E966-86EE-12680CBEE52F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9634,7 +13299,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Prayuda Ari Guntoro Guntoro" refreshedDate="46289.616801736112" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{7A9EEBF8-F762-4C14-887D-117EDE3208E8}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Prayuda Ari Guntoro Guntoro" refreshedDate="46300.394576736115" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{7A9EEBF8-F762-4C14-887D-117EDE3208E8}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table4"/>
   </cacheSource>
@@ -9697,7 +13362,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="DANDORI T." numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="100" maxValue="100"/>
     </cacheField>
     <cacheField name="RUNNING T. " numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -9705,10 +13370,10 @@
     <cacheField name="PRODUCT QTY" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="OPERATING RATE" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    <cacheField name="OPERATING RATE" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="TARGET" numFmtId="0" formula=" 0.8" databaseField="0"/>
+    <cacheField name="TARGET" numFmtId="0" formula="0.85" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -9730,10 +13395,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="1"/>
@@ -9745,10 +13410,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="2"/>
@@ -9760,10 +13425,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="3"/>
@@ -9775,10 +13440,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="4"/>
@@ -9790,10 +13455,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="5"/>
@@ -9805,10 +13470,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="6"/>
@@ -9820,10 +13485,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="7"/>
@@ -9835,10 +13500,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="8"/>
@@ -9850,10 +13515,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="9"/>
@@ -9865,10 +13530,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="10"/>
@@ -9880,10 +13545,10 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <x v="11"/>
@@ -9895,16 +13560,16 @@
     <m/>
     <m/>
     <x v="0"/>
+    <n v="100"/>
     <m/>
     <m/>
-    <m/>
-    <m/>
+    <n v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2768C1A7-CF4D-4B1A-9488-2D606A57C0D6}" name="PivotTable29" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2768C1A7-CF4D-4B1A-9488-2D606A57C0D6}" name="PivotTable29" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="AVG" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B9:O12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -9999,8 +13664,16 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="DANDORI." fld="9" baseField="8" baseItem="0"/>
+    <dataField name="DANDORI T AVG." fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -10014,8 +13687,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CDF4683-225E-491F-BC53-BACA1AD4F4FB}" name="PivotTable23" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="O27:P31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CDF4683-225E-491F-BC53-BACA1AD4F4FB}" name="PivotTable23" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="O27:Q31" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -10070,7 +13743,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
@@ -10090,17 +13763,26 @@
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
   <pageFields count="2">
     <pageField fld="3" item="4" hier="-1"/>
     <pageField fld="4" hier="-1"/>
   </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="6">
+  <chartFormats count="7">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -10155,6 +13837,15 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="19" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -10169,7 +13860,635 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A01F2CE9-B7B1-443F-AC32-A00886791260}" name="PivotTable12" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983F6769-FF4F-45FA-A00D-3D6DA862D39D}" name="PivotTable28" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="FB4:FD7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="5" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221D5A86-0FAF-4D4D-9C44-7BE90E19394D}" name="PivotTable9" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="AT4:AW7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E75A289-3383-4298-8FCC-8F5B4061FFF8}" name="PivotTable22" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="O49:Q53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBEFD717-55D2-4077-BD74-B3665F7BCED5}" name="PivotTable14" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="DX4:DZ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C678E28A-B4DB-4C7B-9C04-D16A9B79A051}" name="PivotTable20" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="B27:D30" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="6" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A01F2CE9-B7B1-443F-AC32-A00886791260}" name="PivotTable12" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="CS4:CU7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -10262,296 +14581,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A90CBD1C-EB98-462C-B899-A137F77093F8}" name="PivotTable13" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="CC4:CF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52385311-543D-48DA-9DB8-077801849FE9}" name="PivotTable24" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
-  <location ref="O5:P9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="1" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <chartFormats count="10">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="38" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="40" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="42" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04461318-0B3E-47A8-BB7B-19F4A3469DF7}" name="PivotTable8" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04461318-0B3E-47A8-BB7B-19F4A3469DF7}" name="PivotTable8" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="AD4:AF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -10644,357 +14675,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6D0FF5-F6F2-4E98-A793-3425B75F1FFE}" name="PivotTable15" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="EM4:EO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A17830ED-8927-4755-8501-7DFC778792DA}" name="PivotTable11" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="DH4:DJ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B55F4480-DCD5-4360-899D-5EEB6809EDFC}" name="PivotTable26" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="O70:P73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="8" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <chartFormats count="7">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{078CD331-B6DD-42D6-A2EA-38A1DC462D3C}" name="PivotTable10" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{078CD331-B6DD-42D6-A2EA-38A1DC462D3C}" name="PivotTable10" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BL4:BO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -11091,8 +14773,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C678E28A-B4DB-4C7B-9C04-D16A9B79A051}" name="PivotTable20" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="B27:C30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32494390-7516-4808-9564-94C6298A0B64}" name="PivotTable25" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="B70:D73" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -11147,7 +14829,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
@@ -11158,23 +14840,62 @@
       <x/>
     </i>
     <i r="1">
-      <x/>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
   <pageFields count="2">
-    <pageField fld="3" item="6" hier="-1"/>
+    <pageField fld="3" item="0" hier="-1"/>
     <pageField fld="4" hier="-1"/>
   </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="6">
+  <formats count="3">
+    <format dxfId="22">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="8">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -11229,6 +14950,24 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="21" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -11243,8 +14982,294 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1099930-AA0D-42B1-B26F-6D33ECEE56A5}" name="PivotTable21" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="B50:C53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A17830ED-8927-4755-8501-7DFC778792DA}" name="PivotTable11" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="DH4:DJ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3913DF35-F900-4B9E-A461-7854FE3E9E8A}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="C7:E21" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="count" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85 %" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="20">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52385311-543D-48DA-9DB8-077801849FE9}" name="PivotTable24" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
+  <location ref="O5:Q9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -11299,7 +15324,310 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="1" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="11">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="38" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="40" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="42" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="42" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6D0FF5-F6F2-4E98-A793-3425B75F1FFE}" name="PivotTable15" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="EM4:EO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="8" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E9197E-66A0-4212-8D82-1C76DDF3FEE7}" name="PivotTable27" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25">
+  <location ref="B92:D95" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
@@ -11310,23 +15638,32 @@
       <x/>
     </i>
     <i r="1">
-      <x v="1"/>
+      <x v="11"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
   <pageFields count="2">
-    <pageField fld="3" item="7" hier="-1"/>
+    <pageField fld="3" item="5" hier="-1"/>
     <pageField fld="4" hier="-1"/>
   </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="6">
+  <chartFormats count="9">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -11381,6 +15718,33 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="21" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -11394,9 +15758,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3913DF35-F900-4B9E-A461-7854FE3E9E8A}" name="PivotTable1" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="C7:D21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1099930-AA0D-42B1-B26F-6D33ECEE56A5}" name="PivotTable21" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="B50:D53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -11422,7 +15786,20 @@
       </items>
     </pivotField>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisPage" showAll="0">
       <items count="3">
         <item m="1" x="1"/>
@@ -11438,87 +15815,43 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="14">
+  <rowItems count="3">
     <i>
-      <x/>
-    </i>
-    <i r="1">
       <x/>
     </i>
     <i r="1">
       <x v="1"/>
     </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
-  <pageFields count="1">
+  <pageFields count="2">
+    <pageField fld="3" item="7" hier="-1"/>
     <pageField fld="4" hier="-1"/>
   </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="count" baseField="0" baseItem="0" numFmtId="166"/>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="2">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="0" selected="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="0">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="4">
+  <chartFormats count="7">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -11528,7 +15861,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="2" format="0" series="1">
+    <chartFormat chart="9" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -11537,7 +15870,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="4" format="0" series="1">
+    <chartFormat chart="10" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -11546,11 +15879,38 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="6" format="0" series="1">
+    <chartFormat chart="16" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -11568,9 +15928,367 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221D5A86-0FAF-4D4D-9C44-7BE90E19394D}" name="PivotTable9" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="AT4:AW7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F2800DD-182C-4C60-A59A-C1128AAB24B1}" name="PivotTable17" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
+  <location ref="B5:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="2" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="38" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="40" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="40" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B55F4480-DCD5-4360-899D-5EEB6809EDFC}" name="PivotTable26" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="O70:Q73" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="8" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A90CBD1C-EB98-462C-B899-A137F77093F8}" name="PivotTable13" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="CC4:CF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
       <items count="13">
@@ -11638,17 +16356,17 @@
   </colFields>
   <colItems count="3">
     <i>
-      <x v="3"/>
+      <x v="5"/>
     </i>
     <i>
-      <x v="6"/>
+      <x v="8"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="3" item="1" hier="-1"/>
+    <pageField fld="3" item="3" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
@@ -11665,874 +16383,27 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983F6769-FF4F-45FA-A00D-3D6DA862D39D}" name="PivotTable28" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="FB4:FD7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="5" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBEFD717-55D2-4077-BD74-B3665F7BCED5}" name="PivotTable14" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="DX4:DZ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F2800DD-182C-4C60-A59A-C1128AAB24B1}" name="PivotTable17" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="42">
-  <location ref="B5:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="2" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <chartFormats count="7">
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="38" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="40" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E75A289-3383-4298-8FCC-8F5B4061FFF8}" name="PivotTable22" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="O49:P53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="3" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E9197E-66A0-4212-8D82-1C76DDF3FEE7}" name="PivotTable27" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="B92:C95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="5" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <chartFormats count="7">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32494390-7516-4808-9564-94C6298A0B64}" name="PivotTable25" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="B70:C73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="0" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="4">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1">
-            <x v="2"/>
-          </reference>
-          <reference field="1" count="0" selected="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="3">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="7">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8771DFAE-D88A-41F3-BFC3-CA435140B509}" name="Table4" displayName="Table4" ref="C2:O14" totalsRowShown="0">
   <autoFilter ref="C2:O14" xr:uid="{8771DFAE-D88A-41F3-BFC3-CA435140B509}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{AA0F4A8A-C024-4FC6-9787-B30556B07C4D}" name="MONTH" dataDxfId="17">
+    <tableColumn id="1" xr3:uid="{AA0F4A8A-C024-4FC6-9787-B30556B07C4D}" name="MONTH" dataDxfId="40">
       <calculatedColumnFormula>TEXT(E3, "mmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A8A40FED-5AE6-4F3B-A482-2DC859CBECE8}" name="YEAR" dataDxfId="16">
+    <tableColumn id="12" xr3:uid="{A8A40FED-5AE6-4F3B-A482-2DC859CBECE8}" name="YEAR" dataDxfId="39">
       <calculatedColumnFormula>TEXT(Table4[[#This Row],[DATE]], "yyyy")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53BAB48D-3DEC-4471-BE46-1798702D2303}" name="DATE" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{66B8BA99-4483-49FA-917F-E23A0082F7AE}" name="MACHINE" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{807EF872-0464-40F2-9E8E-2E197E4E4F0F}" name="ITEM NO" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{62AABD23-67B8-4240-81EE-9690684F857B}" name="ITEM NAME" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{ECC4F505-5088-4655-955E-FFCF79127D17}" name="SPEED (M)" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{88E606BF-77D9-43BC-A245-5060F9FFB2DC}" name="SPEED (H)" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{559CFE2C-A093-4C69-8644-EA4041670421}" name="OPERATOR" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{34427C21-CCE4-495D-849E-C8CE3AAF98F2}" name="DANDORI T." dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{D5BBBED8-248D-4454-BE79-04A39D6BF301}" name="RUNNING T. " dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{B0EFB25E-6FC0-43A9-9EF6-C8CD305D25B8}" name="PRODUCT QTY" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{D9DBE70D-60F1-4AB6-B94B-1334C66C922A}" name="OPERATING RATE" dataDxfId="5">
+    <tableColumn id="2" xr3:uid="{53BAB48D-3DEC-4471-BE46-1798702D2303}" name="DATE" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{66B8BA99-4483-49FA-917F-E23A0082F7AE}" name="MACHINE" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{807EF872-0464-40F2-9E8E-2E197E4E4F0F}" name="ITEM NO" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{62AABD23-67B8-4240-81EE-9690684F857B}" name="ITEM NAME" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{ECC4F505-5088-4655-955E-FFCF79127D17}" name="SPEED (M)" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{88E606BF-77D9-43BC-A245-5060F9FFB2DC}" name="SPEED (H)" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{559CFE2C-A093-4C69-8644-EA4041670421}" name="OPERATOR" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{34427C21-CCE4-495D-849E-C8CE3AAF98F2}" name="DANDORI T." dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{D5BBBED8-248D-4454-BE79-04A39D6BF301}" name="RUNNING T. " dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{B0EFB25E-6FC0-43A9-9EF6-C8CD305D25B8}" name="PRODUCT QTY" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{D9DBE70D-60F1-4AB6-B94B-1334C66C922A}" name="OPERATING RATE" dataDxfId="28">
       <calculatedColumnFormula>IF(Table4[[#This Row],[PRODUCT QTY]] = "", "", Table4[[#This Row],[PRODUCT QTY]]/(Table4[[#This Row],[RUNNING T. ]]*Table4[[#This Row],[SPEED (M)]]))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12860,13 +16731,12 @@
   <dimension ref="B4:O12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.140625" bestFit="1" customWidth="1"/>
@@ -12875,37 +16745,37 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>16</v>
@@ -12951,18 +16821,96 @@
       <c r="N10" t="s">
         <v>29</v>
       </c>
-      <c r="O10" t="s">
-        <v>14</v>
+      <c r="O10" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="C11" s="20">
+        <v>100</v>
+      </c>
+      <c r="D11" s="20">
+        <v>100</v>
+      </c>
+      <c r="E11" s="20">
+        <v>100</v>
+      </c>
+      <c r="F11" s="20">
+        <v>100</v>
+      </c>
+      <c r="G11" s="20">
+        <v>100</v>
+      </c>
+      <c r="H11" s="20">
+        <v>100</v>
+      </c>
+      <c r="I11" s="20">
+        <v>100</v>
+      </c>
+      <c r="J11" s="20">
+        <v>100</v>
+      </c>
+      <c r="K11" s="20">
+        <v>100</v>
+      </c>
+      <c r="L11" s="20">
+        <v>100</v>
+      </c>
+      <c r="M11" s="20">
+        <v>100</v>
+      </c>
+      <c r="N11" s="20">
+        <v>100</v>
+      </c>
+      <c r="O11" s="20">
+        <v>100</v>
+      </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="C12" s="20">
+        <v>100</v>
+      </c>
+      <c r="D12" s="20">
+        <v>100</v>
+      </c>
+      <c r="E12" s="20">
+        <v>100</v>
+      </c>
+      <c r="F12" s="20">
+        <v>100</v>
+      </c>
+      <c r="G12" s="20">
+        <v>100</v>
+      </c>
+      <c r="H12" s="20">
+        <v>100</v>
+      </c>
+      <c r="I12" s="20">
+        <v>100</v>
+      </c>
+      <c r="J12" s="20">
+        <v>100</v>
+      </c>
+      <c r="K12" s="20">
+        <v>100</v>
+      </c>
+      <c r="L12" s="20">
+        <v>100</v>
+      </c>
+      <c r="M12" s="20">
+        <v>100</v>
+      </c>
+      <c r="N12" s="20">
+        <v>100</v>
+      </c>
+      <c r="O12" s="20">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -12982,13 +16930,13 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="38.5703125" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="8" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="37" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -13120,13 +17068,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="P3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="2:160" x14ac:dyDescent="0.25">
@@ -13192,11 +17140,17 @@
       <c r="C5" t="s">
         <v>40</v>
       </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
       <c r="O5" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P5" t="s">
         <v>40</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>50</v>
       </c>
       <c r="AD5" s="10" t="s">
         <v>12</v>
@@ -13293,91 +17247,252 @@
       <c r="B6" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="19"/>
+      <c r="C6" s="16">
+        <v>1</v>
+      </c>
+      <c r="D6" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O6" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="19"/>
+      <c r="P6" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>0.85</v>
+      </c>
       <c r="AD6" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="AE6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="20">
+        <v>1</v>
+      </c>
       <c r="AT6" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="AU6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="20">
+        <v>2</v>
+      </c>
       <c r="BL6" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="BM6" s="20">
+        <v>1</v>
+      </c>
+      <c r="BN6" s="20">
+        <v>1</v>
+      </c>
+      <c r="BO6" s="20">
+        <v>2</v>
+      </c>
       <c r="CC6" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="CD6" s="20">
+        <v>1</v>
+      </c>
+      <c r="CE6" s="20">
+        <v>1</v>
+      </c>
+      <c r="CF6" s="20">
+        <v>2</v>
+      </c>
       <c r="CS6" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="CT6" s="20">
+        <v>1</v>
+      </c>
+      <c r="CU6" s="20">
+        <v>1</v>
+      </c>
       <c r="DH6" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="DI6" s="20">
+        <v>1</v>
+      </c>
+      <c r="DJ6" s="20">
+        <v>1</v>
+      </c>
       <c r="DX6" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="DY6" s="20">
+        <v>1</v>
+      </c>
+      <c r="DZ6" s="20">
+        <v>1</v>
+      </c>
       <c r="EM6" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="EN6" s="20">
+        <v>1</v>
+      </c>
+      <c r="EO6" s="20">
+        <v>1</v>
+      </c>
       <c r="FB6" s="11" t="s">
         <v>13</v>
+      </c>
+      <c r="FC6" s="20">
+        <v>1</v>
+      </c>
+      <c r="FD6" s="20">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:160" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="16">
+        <v>1</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O7" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P7" s="19"/>
+      <c r="P7" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>0.85</v>
+      </c>
       <c r="AD7" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="AE7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="20">
+        <v>1</v>
+      </c>
       <c r="AT7" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="AU7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="20">
+        <v>2</v>
+      </c>
       <c r="BL7" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="BM7" s="20">
+        <v>1</v>
+      </c>
+      <c r="BN7" s="20">
+        <v>1</v>
+      </c>
+      <c r="BO7" s="20">
+        <v>2</v>
+      </c>
       <c r="CC7" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="CD7" s="20">
+        <v>1</v>
+      </c>
+      <c r="CE7" s="20">
+        <v>1</v>
+      </c>
+      <c r="CF7" s="20">
+        <v>2</v>
+      </c>
       <c r="CS7" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="CT7" s="20">
+        <v>1</v>
+      </c>
+      <c r="CU7" s="20">
+        <v>1</v>
+      </c>
       <c r="DH7" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="DI7" s="20">
+        <v>1</v>
+      </c>
+      <c r="DJ7" s="20">
+        <v>1</v>
+      </c>
       <c r="DX7" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="DY7" s="20">
+        <v>1</v>
+      </c>
+      <c r="DZ7" s="20">
+        <v>1</v>
+      </c>
       <c r="EM7" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="EN7" s="20">
+        <v>1</v>
+      </c>
+      <c r="EO7" s="20">
+        <v>1</v>
+      </c>
       <c r="FB7" s="11" t="s">
         <v>14</v>
+      </c>
+      <c r="FC7" s="20">
+        <v>1</v>
+      </c>
+      <c r="FD7" s="20">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:160" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="16">
+        <v>1</v>
+      </c>
+      <c r="D8" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="P8" s="19"/>
+      <c r="P8" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="9" spans="2:160" x14ac:dyDescent="0.25">
       <c r="O9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P9" s="19"/>
+      <c r="P9" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
@@ -13406,13 +17521,13 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>2</v>
       </c>
       <c r="P25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
@@ -13422,48 +17537,89 @@
       <c r="C27" t="s">
         <v>40</v>
       </c>
+      <c r="D27" t="s">
+        <v>50</v>
+      </c>
       <c r="O27" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P27" t="s">
         <v>40</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="19"/>
+      <c r="C28" s="16">
+        <v>1</v>
+      </c>
+      <c r="D28" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O28" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="P28" s="19"/>
+      <c r="P28" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="19"/>
+      <c r="C29" s="16">
+        <v>1</v>
+      </c>
+      <c r="D29" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O29" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="P29" s="19"/>
+      <c r="P29" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="19"/>
+      <c r="C30" s="16">
+        <v>1</v>
+      </c>
+      <c r="D30" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O30" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="P30" s="19"/>
+      <c r="P30" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="O31" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P31" s="19"/>
+      <c r="P31" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E46" t="str">
@@ -13492,7 +17648,7 @@
         <v>2</v>
       </c>
       <c r="P47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
@@ -13500,58 +17656,99 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O49" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P49" t="s">
         <v>40</v>
       </c>
+      <c r="Q49" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C50" t="s">
         <v>40</v>
       </c>
+      <c r="D50" t="s">
+        <v>50</v>
+      </c>
       <c r="O50" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="P50" s="19"/>
+      <c r="P50" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="19"/>
+      <c r="C51" s="16">
+        <v>1</v>
+      </c>
+      <c r="D51" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O51" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="P51" s="19"/>
+      <c r="P51" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="19"/>
+      <c r="C52" s="16">
+        <v>1</v>
+      </c>
+      <c r="D52" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O52" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="P52" s="19"/>
+      <c r="P52" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="19"/>
+      <c r="C53" s="16">
+        <v>1</v>
+      </c>
+      <c r="D53" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O53" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P53" s="19"/>
+      <c r="P53" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B67" s="10" t="s">
@@ -13580,13 +17777,13 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O68" s="10" t="s">
         <v>2</v>
       </c>
       <c r="P68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.25">
@@ -13596,42 +17793,78 @@
       <c r="C70" t="s">
         <v>40</v>
       </c>
+      <c r="D70" t="s">
+        <v>50</v>
+      </c>
       <c r="O70" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P70" t="s">
         <v>40</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B71" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C71" s="19"/>
+      <c r="C71" s="16">
+        <v>1</v>
+      </c>
+      <c r="D71" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O71" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="P71" s="19"/>
+      <c r="P71" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B72" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C72" s="19"/>
+      <c r="C72" s="16">
+        <v>1</v>
+      </c>
+      <c r="D72" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O72" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="P72" s="19"/>
+      <c r="P72" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B73" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="19"/>
+      <c r="C73" s="16">
+        <v>1</v>
+      </c>
+      <c r="D73" s="20">
+        <v>0.85</v>
+      </c>
       <c r="O73" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P73" s="19"/>
+      <c r="P73" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" s="10" t="s">
@@ -13650,7 +17883,7 @@
         <v>2</v>
       </c>
       <c r="C90" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.25">
@@ -13660,145 +17893,251 @@
       <c r="C92" t="s">
         <v>40</v>
       </c>
+      <c r="D92" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B93" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C93" s="19"/>
+      <c r="C93" s="16">
+        <v>1</v>
+      </c>
+      <c r="D93" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B94" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C94" s="19"/>
+      <c r="C94" s="16">
+        <v>1</v>
+      </c>
+      <c r="D94" s="20">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C95" s="19"/>
+      <c r="C95" s="16">
+        <v>1</v>
+      </c>
+      <c r="D95" s="20">
+        <v>0.85</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C17C2FC-B423-40AA-AB87-06D0390D0599}">
-  <dimension ref="C5:E21"/>
+  <dimension ref="C2:L21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C5" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D7" t="s">
         <v>40</v>
       </c>
+      <c r="E7" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="19"/>
+      <c r="D8" s="16">
+        <v>12</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="19"/>
+      <c r="D9" s="16">
+        <v>1</v>
+      </c>
+      <c r="E9" s="16">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="19"/>
+      <c r="D10" s="16">
+        <v>1</v>
+      </c>
+      <c r="E10" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C11" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="16">
+        <v>1</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C12" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="19"/>
+      <c r="D12" s="16">
+        <v>1</v>
+      </c>
+      <c r="E12" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="19"/>
+      <c r="D13" s="16">
+        <v>1</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C14" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="19"/>
+      <c r="D14" s="16">
+        <v>1</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="16">
+        <v>1</v>
+      </c>
+      <c r="E15" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="19"/>
+      <c r="D16" s="16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C17" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="19"/>
+      <c r="D17" s="16">
+        <v>1</v>
+      </c>
+      <c r="E17" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C18" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="19"/>
+      <c r="D18" s="16">
+        <v>1</v>
+      </c>
+      <c r="E18" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="19"/>
+      <c r="D19" s="16">
+        <v>1</v>
+      </c>
+      <c r="E19" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C20" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="19"/>
+      <c r="D20" s="16">
+        <v>1</v>
+      </c>
+      <c r="E20" s="20">
+        <v>0.85</v>
+      </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C21" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="19"/>
+      <c r="D21" s="16">
+        <v>12</v>
+      </c>
+      <c r="E21" s="20">
+        <v>0.85</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F2:L2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -13820,7 +18159,8 @@
     <col min="7" max="7" width="36.7109375" customWidth="1"/>
     <col min="8" max="8" width="45.140625" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
     <col min="12" max="12" width="14.140625" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" customWidth="1"/>
     <col min="14" max="14" width="16.140625" customWidth="1"/>
@@ -13828,11 +18168,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
@@ -13896,9 +18236,13 @@
       <c r="H3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>100</v>
+      </c>
       <c r="M3" s="3"/>
-      <c r="O3" s="18"/>
+      <c r="O3" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="13"/>
@@ -13921,10 +18265,14 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <v>100</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="18"/>
+      <c r="O4" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
@@ -13947,10 +18295,14 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>100</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="18"/>
+      <c r="O5" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
@@ -13973,10 +18325,14 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>100</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="18"/>
+      <c r="O6" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="13"/>
@@ -13999,10 +18355,14 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>100</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="18"/>
+      <c r="O7" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
@@ -14025,10 +18385,14 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="L8" s="3">
+        <v>100</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="18"/>
+      <c r="O8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="13"/>
@@ -14051,10 +18415,14 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="L9" s="3">
+        <v>100</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="18"/>
+      <c r="O9" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="13"/>
@@ -14077,10 +18445,14 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="L10" s="3">
+        <v>100</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="18"/>
+      <c r="O10" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="13"/>
@@ -14103,10 +18475,14 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="L11" s="3">
+        <v>100</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="18"/>
+      <c r="O11" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="13"/>
@@ -14129,10 +18505,14 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>100</v>
+      </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="18"/>
+      <c r="O12" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="13"/>
@@ -14155,10 +18535,14 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <v>100</v>
+      </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="18"/>
+      <c r="O13" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="13"/>
@@ -14181,10 +18565,14 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>100</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="18"/>
+      <c r="O14" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
@@ -14196,6 +18584,9 @@
     <mergeCell ref="E1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="O3 O4:O14" calculatedColumn="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/src/lib/template/achievements-template.xlsx
+++ b/src/lib/template/achievements-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\TOHO(Fajar)\KCF\MC Monitoring System\kcf-mc-monitoring\src\lib\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FF9F06-1F61-46D9-8A77-85892EB9301A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6A5562-ED9B-4105-9090-0FC019AC20A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{370BB547-A0D3-4CB2-B344-9D3804543135}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{370BB547-A0D3-4CB2-B344-9D3804543135}"/>
   </bookViews>
   <sheets>
     <sheet name="OPERATOR" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="47">
   <si>
     <t>DATE</t>
   </si>
@@ -185,19 +185,7 @@
     <t>(All)</t>
   </si>
   <si>
-    <t>DANDORI T AVG.</t>
-  </si>
-  <si>
-    <t>AVG</t>
-  </si>
-  <si>
     <t>PRODUKTIFITAS PRODUKSI</t>
-  </si>
-  <si>
-    <t>TARGET 85 %</t>
-  </si>
-  <si>
-    <t>TARGET 85%</t>
   </si>
 </sst>
 </file>
@@ -312,7 +300,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -356,11 +344,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -369,85 +356,7 @@
     <cellStyle name="60% - Accent6" xfId="2" builtinId="52"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0%"/>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0%"/>
     </dxf>
@@ -705,6 +614,18 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -839,6 +760,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -896,6 +820,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1007,7 +934,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1032,7 +959,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1144,72 +1071,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$E$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$E$2</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Oct</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$E$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-8205-4FE0-84FA-47646E5DFA68}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -1278,6 +1139,7 @@
         <c:axId val="719723791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1643,7 +1505,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1763,135 +1625,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'TOTAL RATE'!$E$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85 %</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'TOTAL RATE'!$C$8:$C$21</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="12"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Jan</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Feb</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Mar</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Apr</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>May</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Jun</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Jul</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Aug</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Sep</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>Oct</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Nov</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Dec</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'TOTAL RATE'!$E$8:$E$21</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-311B-4504-96A1-F56A813C4347}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -1959,6 +1692,7 @@
         <c:axId val="719682031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2231,6 +1965,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2332,7 +2069,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -2357,7 +2094,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2475,78 +2212,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$R$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$R$2</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="2"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Jun</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Sep</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$R$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7474-4845-8AE0-346C2BA91012}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -2615,6 +2280,7 @@
         <c:axId val="719646511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2887,6 +2553,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2998,7 +2667,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -3023,7 +2692,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3135,72 +2804,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$E$24</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$E$24</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Jan</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$E$24</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C8E9-4475-9990-8ECB2A2AA79C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -3269,6 +2872,7 @@
         <c:axId val="719687791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -3541,6 +3145,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -3652,7 +3259,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -3677,7 +3284,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3789,72 +3396,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$E$46</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$E$46</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Feb</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$E$46</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-ABBE-44CF-8CC9-12380C06D757}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -3923,6 +3464,7 @@
         <c:axId val="719629711"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4195,6 +3737,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4306,7 +3851,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -4331,7 +3876,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4443,72 +3988,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$E$67</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$E$67</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Mar</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$E$67</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A0F7-418E-9FC0-27D7FC2807A4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -4577,6 +4056,7 @@
         <c:axId val="719681551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4849,6 +4329,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4960,7 +4443,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -4985,7 +4468,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5103,78 +4586,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$R$24</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$R$24</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="2"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>May</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Aug</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$R$24</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-FE4A-4607-9E05-654003A53AB6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -5243,6 +4654,7 @@
         <c:axId val="719711311"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -5515,6 +4927,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5626,7 +5041,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -5651,7 +5066,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5769,78 +5184,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$R$46</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$R$46</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="2"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Apr</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Jul</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$R$46</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-46CB-4242-A579-73626F7AF683}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -5909,6 +5252,7 @@
         <c:axId val="719634031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -6181,6 +5525,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6292,7 +5639,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -6317,7 +5664,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6429,72 +5776,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$R$67</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$R$67</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Nov</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$R$67</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7FB7-412B-ADC6-7C89B79BE3CB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -6563,6 +5844,7 @@
         <c:axId val="719705071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -6835,6 +6117,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6946,7 +6231,7 @@
           </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -6971,7 +6256,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>RATE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7083,72 +6368,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'RATE FORGING'!$E$89</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TARGET 85%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'RATE FORGING'!$E$89</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="1"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Dec</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2026</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'RATE FORGING'!$E$89</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.85</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-668A-446B-AD34-F91B3FF10546}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
@@ -7217,6 +6436,7 @@
         <c:axId val="121995600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -13569,126 +12789,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2768C1A7-CF4D-4B1A-9488-2D606A57C0D6}" name="PivotTable29" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="AVG" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B9:O12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="DANDORI T AVG." fld="9" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CDF4683-225E-491F-BC53-BACA1AD4F4FB}" name="PivotTable23" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="O27:Q31" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1099930-AA0D-42B1-B26F-6D33ECEE56A5}" name="PivotTable21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="B50:C53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -13743,45 +12845,300 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="3">
     <i>
       <x/>
     </i>
     <i r="1">
-      <x v="4"/>
+      <x v="1"/>
     </i>
-    <i r="1">
-      <x v="7"/>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="7" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6D0FF5-F6F2-4E98-A793-3425B75F1FFE}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="EM4:EO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="-2"/>
+    <field x="0"/>
   </colFields>
   <colItems count="2">
     <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
       <x/>
     </i>
-    <i i="1">
-      <x v="1"/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="8" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32494390-7516-4808-9564-94C6298A0B64}" name="PivotTable25" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="B70:C73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
     </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
   </colItems>
   <pageFields count="2">
-    <pageField fld="3" item="4" hier="-1"/>
+    <pageField fld="3" item="0" hier="-1"/>
     <pageField fld="4" hier="-1"/>
   </pageFields>
-  <dataFields count="2">
+  <dataFields count="1">
     <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="18">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <chartFormats count="7">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -13837,11 +13194,11 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="19" format="2" series="1">
+    <chartFormat chart="21" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -13859,8 +13216,676 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983F6769-FF4F-45FA-A00D-3D6DA862D39D}" name="PivotTable28" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBEFD717-55D2-4077-BD74-B3665F7BCED5}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="DX4:DZ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A90CBD1C-EB98-462C-B899-A137F77093F8}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="CC4:CF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C678E28A-B4DB-4C7B-9C04-D16A9B79A051}" name="PivotTable20" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="B27:C30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="6" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CDF4683-225E-491F-BC53-BACA1AD4F4FB}" name="PivotTable23" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="O27:P31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="4" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E9197E-66A0-4212-8D82-1C76DDF3FEE7}" name="PivotTable27" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25">
+  <location ref="B92:C95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="5" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983F6769-FF4F-45FA-A00D-3D6DA862D39D}" name="PivotTable28" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="FB4:FD7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -13953,8 +13978,276 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221D5A86-0FAF-4D4D-9C44-7BE90E19394D}" name="PivotTable9" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A01F2CE9-B7B1-443F-AC32-A00886791260}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="CS4:CU7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3913DF35-F900-4B9E-A461-7854FE3E9E8A}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="C7:D21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="count" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="16">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221D5A86-0FAF-4D4D-9C44-7BE90E19394D}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="AT4:AW7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -14050,9 +14343,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E75A289-3383-4298-8FCC-8F5B4061FFF8}" name="PivotTable22" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="O49:Q53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F2800DD-182C-4C60-A59A-C1128AAB24B1}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
+  <location ref="B5:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -14107,64 +14400,34 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="3">
     <i>
       <x/>
     </i>
     <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
+      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
   <pageFields count="2">
-    <pageField fld="3" item="3" hier="-1"/>
+    <pageField fld="3" item="2" hier="-1"/>
     <pageField fld="4" hier="-1"/>
   </pageFields>
-  <dataFields count="2">
+  <dataFields count="1">
     <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="7">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
     <chartFormat chart="10" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -14183,7 +14446,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
+    <chartFormat chart="24" format="8" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14192,7 +14455,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
+    <chartFormat chart="37" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14201,11 +14464,29 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="19" format="2" series="1">
+    <chartFormat chart="38" format="8" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="40" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -14223,9 +14504,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBEFD717-55D2-4077-BD74-B3665F7BCED5}" name="PivotTable14" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="DX4:DZ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A17830ED-8927-4755-8501-7DFC778792DA}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="DH4:DJ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
       <items count="13">
@@ -14293,14 +14574,14 @@
   </colFields>
   <colItems count="2">
     <i>
-      <x v="1"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="3" item="7" hier="-1"/>
+    <pageField fld="3" item="6" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
@@ -14317,272 +14598,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C678E28A-B4DB-4C7B-9C04-D16A9B79A051}" name="PivotTable20" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="B27:D30" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="6" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="7">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A01F2CE9-B7B1-443F-AC32-A00886791260}" name="PivotTable12" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="CS4:CU7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04461318-0B3E-47A8-BB7B-19F4A3469DF7}" name="PivotTable8" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04461318-0B3E-47A8-BB7B-19F4A3469DF7}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="AD4:AF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -14675,8 +14692,199 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{078CD331-B6DD-42D6-A2EA-38A1DC462D3C}" name="PivotTable10" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52385311-543D-48DA-9DB8-077801849FE9}" name="PivotTable24" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
+  <location ref="O5:P9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="1" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="10">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="38" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="40" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="42" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{078CD331-B6DD-42D6-A2EA-38A1DC462D3C}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BL4:BO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
@@ -14772,9 +14980,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32494390-7516-4808-9564-94C6298A0B64}" name="PivotTable25" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="B70:D73" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E75A289-3383-4298-8FCC-8F5B4061FFF8}" name="PivotTable22" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="O49:P53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
@@ -14829,7 +15037,162 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="3" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B55F4480-DCD5-4360-899D-5EEB6809EDFC}" name="PivotTable26" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="O70:P73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
@@ -14840,62 +15203,23 @@
       <x/>
     </i>
     <i r="1">
-      <x v="2"/>
+      <x v="10"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
   <pageFields count="2">
-    <pageField fld="3" item="0" hier="-1"/>
+    <pageField fld="3" item="8" hier="-1"/>
     <pageField fld="4" hier="-1"/>
   </pageFields>
-  <dataFields count="2">
+  <dataFields count="1">
     <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="3">
-    <format dxfId="22">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1">
-            <x v="2"/>
-          </reference>
-          <reference field="1" count="0" selected="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="23">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="14">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="8">
+  <chartFormats count="7">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -14959,1418 +15283,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="21" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A17830ED-8927-4755-8501-7DFC778792DA}" name="PivotTable11" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="DH4:DJ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3913DF35-F900-4B9E-A461-7854FE3E9E8A}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="C7:E21" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="RATE" fld="12" subtotal="count" baseField="0" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85 %" fld="13" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="20">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="0" selected="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="21">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="5">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52385311-543D-48DA-9DB8-077801849FE9}" name="PivotTable24" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
-  <location ref="O5:Q9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="1" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="11">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="38" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="40" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="42" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="42" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6D0FF5-F6F2-4E98-A793-3425B75F1FFE}" name="PivotTable15" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="EM4:EO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E9197E-66A0-4212-8D82-1C76DDF3FEE7}" name="PivotTable27" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25">
-  <location ref="B92:D95" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="5" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="23" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="23" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1099930-AA0D-42B1-B26F-6D33ECEE56A5}" name="PivotTable21" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="B50:D53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="7" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="7">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F2800DD-182C-4C60-A59A-C1128AAB24B1}" name="PivotTable17" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
-  <location ref="B5:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="2" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="38" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="40" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="40" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B55F4480-DCD5-4360-899D-5EEB6809EDFC}" name="PivotTable26" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="O70:Q73" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="8" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-    <dataField name="TARGET 85%" fld="13" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A90CBD1C-EB98-462C-B899-A137F77093F8}" name="PivotTable13" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="CC4:CF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -16387,23 +15300,23 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8771DFAE-D88A-41F3-BFC3-CA435140B509}" name="Table4" displayName="Table4" ref="C2:O14" totalsRowShown="0">
   <autoFilter ref="C2:O14" xr:uid="{8771DFAE-D88A-41F3-BFC3-CA435140B509}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{AA0F4A8A-C024-4FC6-9787-B30556B07C4D}" name="MONTH" dataDxfId="40">
+    <tableColumn id="1" xr3:uid="{AA0F4A8A-C024-4FC6-9787-B30556B07C4D}" name="MONTH" dataDxfId="14">
       <calculatedColumnFormula>TEXT(E3, "mmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A8A40FED-5AE6-4F3B-A482-2DC859CBECE8}" name="YEAR" dataDxfId="39">
+    <tableColumn id="12" xr3:uid="{A8A40FED-5AE6-4F3B-A482-2DC859CBECE8}" name="YEAR" dataDxfId="13">
       <calculatedColumnFormula>TEXT(Table4[[#This Row],[DATE]], "yyyy")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53BAB48D-3DEC-4471-BE46-1798702D2303}" name="DATE" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{66B8BA99-4483-49FA-917F-E23A0082F7AE}" name="MACHINE" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{807EF872-0464-40F2-9E8E-2E197E4E4F0F}" name="ITEM NO" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{62AABD23-67B8-4240-81EE-9690684F857B}" name="ITEM NAME" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{ECC4F505-5088-4655-955E-FFCF79127D17}" name="SPEED (M)" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{88E606BF-77D9-43BC-A245-5060F9FFB2DC}" name="SPEED (H)" dataDxfId="33"/>
-    <tableColumn id="13" xr3:uid="{559CFE2C-A093-4C69-8644-EA4041670421}" name="OPERATOR" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{34427C21-CCE4-495D-849E-C8CE3AAF98F2}" name="DANDORI T." dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{D5BBBED8-248D-4454-BE79-04A39D6BF301}" name="RUNNING T. " dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{B0EFB25E-6FC0-43A9-9EF6-C8CD305D25B8}" name="PRODUCT QTY" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{D9DBE70D-60F1-4AB6-B94B-1334C66C922A}" name="OPERATING RATE" dataDxfId="28">
+    <tableColumn id="2" xr3:uid="{53BAB48D-3DEC-4471-BE46-1798702D2303}" name="DATE" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{66B8BA99-4483-49FA-917F-E23A0082F7AE}" name="MACHINE" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{807EF872-0464-40F2-9E8E-2E197E4E4F0F}" name="ITEM NO" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{62AABD23-67B8-4240-81EE-9690684F857B}" name="ITEM NAME" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{ECC4F505-5088-4655-955E-FFCF79127D17}" name="SPEED (M)" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{88E606BF-77D9-43BC-A245-5060F9FFB2DC}" name="SPEED (H)" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{559CFE2C-A093-4C69-8644-EA4041670421}" name="OPERATOR" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{34427C21-CCE4-495D-849E-C8CE3AAF98F2}" name="DANDORI T." dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{D5BBBED8-248D-4454-BE79-04A39D6BF301}" name="RUNNING T. " dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{B0EFB25E-6FC0-43A9-9EF6-C8CD305D25B8}" name="PRODUCT QTY" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{D9DBE70D-60F1-4AB6-B94B-1334C66C922A}" name="OPERATING RATE" dataDxfId="2">
       <calculatedColumnFormula>IF(Table4[[#This Row],[PRODUCT QTY]] = "", "", Table4[[#This Row],[PRODUCT QTY]]/(Table4[[#This Row],[RUNNING T. ]]*Table4[[#This Row],[SPEED (M)]]))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16728,7 +15641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2067F42-980B-4ACC-98D8-189DCD67ED8A}">
-  <dimension ref="B4:O12"/>
+  <dimension ref="B4:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -16744,7 +15657,7 @@
     <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="18" t="s">
         <v>44</v>
       </c>
@@ -16755,7 +15668,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -16764,7 +15677,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -16772,146 +15685,6 @@
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="20">
-        <v>100</v>
-      </c>
-      <c r="D11" s="20">
-        <v>100</v>
-      </c>
-      <c r="E11" s="20">
-        <v>100</v>
-      </c>
-      <c r="F11" s="20">
-        <v>100</v>
-      </c>
-      <c r="G11" s="20">
-        <v>100</v>
-      </c>
-      <c r="H11" s="20">
-        <v>100</v>
-      </c>
-      <c r="I11" s="20">
-        <v>100</v>
-      </c>
-      <c r="J11" s="20">
-        <v>100</v>
-      </c>
-      <c r="K11" s="20">
-        <v>100</v>
-      </c>
-      <c r="L11" s="20">
-        <v>100</v>
-      </c>
-      <c r="M11" s="20">
-        <v>100</v>
-      </c>
-      <c r="N11" s="20">
-        <v>100</v>
-      </c>
-      <c r="O11" s="20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="20">
-        <v>100</v>
-      </c>
-      <c r="D12" s="20">
-        <v>100</v>
-      </c>
-      <c r="E12" s="20">
-        <v>100</v>
-      </c>
-      <c r="F12" s="20">
-        <v>100</v>
-      </c>
-      <c r="G12" s="20">
-        <v>100</v>
-      </c>
-      <c r="H12" s="20">
-        <v>100</v>
-      </c>
-      <c r="I12" s="20">
-        <v>100</v>
-      </c>
-      <c r="J12" s="20">
-        <v>100</v>
-      </c>
-      <c r="K12" s="20">
-        <v>100</v>
-      </c>
-      <c r="L12" s="20">
-        <v>100</v>
-      </c>
-      <c r="M12" s="20">
-        <v>100</v>
-      </c>
-      <c r="N12" s="20">
-        <v>100</v>
-      </c>
-      <c r="O12" s="20">
-        <v>100</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16935,7 +15708,7 @@
     <col min="5" max="5" width="38.5703125" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="37" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -17140,17 +15913,11 @@
       <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
       <c r="O5" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P5" t="s">
         <v>40</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>50</v>
       </c>
       <c r="AD5" s="10" t="s">
         <v>12</v>
@@ -17250,106 +16017,100 @@
       <c r="C6" s="16">
         <v>1</v>
       </c>
-      <c r="D6" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O6" s="11" t="s">
         <v>43</v>
       </c>
       <c r="P6" s="16">
         <v>1</v>
       </c>
-      <c r="Q6" s="20">
-        <v>0.85</v>
-      </c>
       <c r="AD6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AE6" s="20">
+      <c r="AE6">
         <v>1</v>
       </c>
-      <c r="AF6" s="20">
+      <c r="AF6">
         <v>1</v>
       </c>
       <c r="AT6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AU6" s="20">
+      <c r="AU6">
         <v>1</v>
       </c>
-      <c r="AV6" s="20">
+      <c r="AV6">
         <v>1</v>
       </c>
-      <c r="AW6" s="20">
+      <c r="AW6">
         <v>2</v>
       </c>
       <c r="BL6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="BM6" s="20">
+      <c r="BM6">
         <v>1</v>
       </c>
-      <c r="BN6" s="20">
+      <c r="BN6">
         <v>1</v>
       </c>
-      <c r="BO6" s="20">
+      <c r="BO6">
         <v>2</v>
       </c>
       <c r="CC6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="CD6" s="20">
+      <c r="CD6">
         <v>1</v>
       </c>
-      <c r="CE6" s="20">
+      <c r="CE6">
         <v>1</v>
       </c>
-      <c r="CF6" s="20">
+      <c r="CF6">
         <v>2</v>
       </c>
       <c r="CS6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="CT6" s="20">
+      <c r="CT6">
         <v>1</v>
       </c>
-      <c r="CU6" s="20">
+      <c r="CU6">
         <v>1</v>
       </c>
       <c r="DH6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="DI6" s="20">
+      <c r="DI6">
         <v>1</v>
       </c>
-      <c r="DJ6" s="20">
+      <c r="DJ6">
         <v>1</v>
       </c>
       <c r="DX6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="DY6" s="20">
+      <c r="DY6">
         <v>1</v>
       </c>
-      <c r="DZ6" s="20">
+      <c r="DZ6">
         <v>1</v>
       </c>
       <c r="EM6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="EN6" s="20">
+      <c r="EN6">
         <v>1</v>
       </c>
-      <c r="EO6" s="20">
+      <c r="EO6">
         <v>1</v>
       </c>
       <c r="FB6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="FC6" s="20">
+      <c r="FC6">
         <v>1</v>
       </c>
-      <c r="FD6" s="20">
+      <c r="FD6">
         <v>1</v>
       </c>
     </row>
@@ -17360,106 +16121,100 @@
       <c r="C7" s="16">
         <v>1</v>
       </c>
-      <c r="D7" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O7" s="14" t="s">
         <v>36</v>
       </c>
       <c r="P7" s="16">
         <v>1</v>
       </c>
-      <c r="Q7" s="20">
-        <v>0.85</v>
-      </c>
       <c r="AD7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AE7" s="20">
+      <c r="AE7">
         <v>1</v>
       </c>
-      <c r="AF7" s="20">
+      <c r="AF7">
         <v>1</v>
       </c>
       <c r="AT7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AU7" s="20">
+      <c r="AU7">
         <v>1</v>
       </c>
-      <c r="AV7" s="20">
+      <c r="AV7">
         <v>1</v>
       </c>
-      <c r="AW7" s="20">
+      <c r="AW7">
         <v>2</v>
       </c>
       <c r="BL7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="BM7" s="20">
+      <c r="BM7">
         <v>1</v>
       </c>
-      <c r="BN7" s="20">
+      <c r="BN7">
         <v>1</v>
       </c>
-      <c r="BO7" s="20">
+      <c r="BO7">
         <v>2</v>
       </c>
       <c r="CC7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="CD7" s="20">
+      <c r="CD7">
         <v>1</v>
       </c>
-      <c r="CE7" s="20">
+      <c r="CE7">
         <v>1</v>
       </c>
-      <c r="CF7" s="20">
+      <c r="CF7">
         <v>2</v>
       </c>
       <c r="CS7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="CT7" s="20">
+      <c r="CT7">
         <v>1</v>
       </c>
-      <c r="CU7" s="20">
+      <c r="CU7">
         <v>1</v>
       </c>
       <c r="DH7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="DI7" s="20">
+      <c r="DI7">
         <v>1</v>
       </c>
-      <c r="DJ7" s="20">
+      <c r="DJ7">
         <v>1</v>
       </c>
       <c r="DX7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="DY7" s="20">
+      <c r="DY7">
         <v>1</v>
       </c>
-      <c r="DZ7" s="20">
+      <c r="DZ7">
         <v>1</v>
       </c>
       <c r="EM7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="EN7" s="20">
+      <c r="EN7">
         <v>1</v>
       </c>
-      <c r="EO7" s="20">
+      <c r="EO7">
         <v>1</v>
       </c>
       <c r="FB7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="FC7" s="20">
+      <c r="FC7">
         <v>1</v>
       </c>
-      <c r="FD7" s="20">
+      <c r="FD7">
         <v>1</v>
       </c>
     </row>
@@ -17470,17 +16225,11 @@
       <c r="C8" s="16">
         <v>1</v>
       </c>
-      <c r="D8" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O8" s="14" t="s">
         <v>31</v>
       </c>
       <c r="P8" s="16">
         <v>1</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="9" spans="2:160" x14ac:dyDescent="0.25">
@@ -17490,9 +16239,6 @@
       <c r="P9" s="16">
         <v>1</v>
       </c>
-      <c r="Q9" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
@@ -17537,17 +16283,11 @@
       <c r="C27" t="s">
         <v>40</v>
       </c>
-      <c r="D27" t="s">
-        <v>50</v>
-      </c>
       <c r="O27" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P27" t="s">
         <v>40</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
@@ -17557,17 +16297,11 @@
       <c r="C28" s="16">
         <v>1</v>
       </c>
-      <c r="D28" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O28" s="11" t="s">
         <v>43</v>
       </c>
       <c r="P28" s="16">
         <v>1</v>
-      </c>
-      <c r="Q28" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
@@ -17577,17 +16311,11 @@
       <c r="C29" s="16">
         <v>1</v>
       </c>
-      <c r="D29" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O29" s="14" t="s">
         <v>37</v>
       </c>
       <c r="P29" s="16">
         <v>1</v>
-      </c>
-      <c r="Q29" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
@@ -17597,17 +16325,11 @@
       <c r="C30" s="16">
         <v>1</v>
       </c>
-      <c r="D30" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O30" s="14" t="s">
         <v>30</v>
       </c>
       <c r="P30" s="16">
         <v>1</v>
-      </c>
-      <c r="Q30" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
@@ -17616,9 +16338,6 @@
       </c>
       <c r="P31" s="16">
         <v>1</v>
-      </c>
-      <c r="Q31" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
@@ -17659,95 +16378,68 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="O49" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P49" t="s">
         <v>40</v>
       </c>
-      <c r="Q49" t="s">
-        <v>50</v>
-      </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C50" t="s">
         <v>40</v>
       </c>
-      <c r="D50" t="s">
-        <v>50</v>
-      </c>
       <c r="O50" s="11" t="s">
         <v>43</v>
       </c>
       <c r="P50" s="16">
         <v>1</v>
       </c>
-      <c r="Q50" s="20">
-        <v>0.85</v>
-      </c>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="11" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="16">
         <v>1</v>
       </c>
-      <c r="D51" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O51" s="14" t="s">
         <v>38</v>
       </c>
       <c r="P51" s="16">
         <v>1</v>
       </c>
-      <c r="Q51" s="20">
-        <v>0.85</v>
-      </c>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C52" s="16">
         <v>1</v>
       </c>
-      <c r="D52" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O52" s="14" t="s">
         <v>19</v>
       </c>
       <c r="P52" s="16">
         <v>1</v>
       </c>
-      <c r="Q52" s="20">
-        <v>0.85</v>
-      </c>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C53" s="16">
         <v>1</v>
       </c>
-      <c r="D53" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O53" s="11" t="s">
         <v>14</v>
       </c>
       <c r="P53" s="16">
         <v>1</v>
-      </c>
-      <c r="Q53" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.25">
@@ -17793,17 +16485,11 @@
       <c r="C70" t="s">
         <v>40</v>
       </c>
-      <c r="D70" t="s">
-        <v>50</v>
-      </c>
       <c r="O70" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P70" t="s">
         <v>40</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.25">
@@ -17813,17 +16499,11 @@
       <c r="C71" s="16">
         <v>1</v>
       </c>
-      <c r="D71" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O71" s="11" t="s">
         <v>43</v>
       </c>
       <c r="P71" s="16">
         <v>1</v>
-      </c>
-      <c r="Q71" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.25">
@@ -17833,17 +16513,11 @@
       <c r="C72" s="16">
         <v>1</v>
       </c>
-      <c r="D72" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O72" s="14" t="s">
         <v>39</v>
       </c>
       <c r="P72" s="16">
         <v>1</v>
-      </c>
-      <c r="Q72" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.25">
@@ -17853,17 +16527,11 @@
       <c r="C73" s="16">
         <v>1</v>
       </c>
-      <c r="D73" s="20">
-        <v>0.85</v>
-      </c>
       <c r="O73" s="11" t="s">
         <v>14</v>
       </c>
       <c r="P73" s="16">
         <v>1</v>
-      </c>
-      <c r="Q73" s="20">
-        <v>0.85</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.25">
@@ -17893,9 +16561,6 @@
       <c r="C92" t="s">
         <v>40</v>
       </c>
-      <c r="D92" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B93" s="11" t="s">
@@ -17904,9 +16569,6 @@
       <c r="C93" s="16">
         <v>1</v>
       </c>
-      <c r="D93" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B94" s="14" t="s">
@@ -17915,9 +16577,6 @@
       <c r="C94" s="16">
         <v>1</v>
       </c>
-      <c r="D94" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95" s="11" t="s">
@@ -17925,9 +16584,6 @@
       </c>
       <c r="C95" s="16">
         <v>1</v>
-      </c>
-      <c r="D95" s="20">
-        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -17951,15 +16607,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F2" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
+      <c r="F2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C5" s="10" t="s">
@@ -17976,9 +16632,6 @@
       <c r="D7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C8" s="11" t="s">
@@ -17987,9 +16640,6 @@
       <c r="D8" s="16">
         <v>12</v>
       </c>
-      <c r="E8" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="9" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C9" s="14" t="s">
@@ -17998,9 +16648,6 @@
       <c r="D9" s="16">
         <v>1</v>
       </c>
-      <c r="E9" s="16">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="10" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C10" s="14" t="s">
@@ -18009,9 +16656,6 @@
       <c r="D10" s="16">
         <v>1</v>
       </c>
-      <c r="E10" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="11" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C11" s="14" t="s">
@@ -18020,9 +16664,6 @@
       <c r="D11" s="16">
         <v>1</v>
       </c>
-      <c r="E11" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C12" s="14" t="s">
@@ -18031,9 +16672,6 @@
       <c r="D12" s="16">
         <v>1</v>
       </c>
-      <c r="E12" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="13" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
@@ -18042,9 +16680,6 @@
       <c r="D13" s="16">
         <v>1</v>
       </c>
-      <c r="E13" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="14" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C14" s="14" t="s">
@@ -18053,9 +16688,6 @@
       <c r="D14" s="16">
         <v>1</v>
       </c>
-      <c r="E14" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
@@ -18064,9 +16696,6 @@
       <c r="D15" s="16">
         <v>1</v>
       </c>
-      <c r="E15" s="20">
-        <v>0.85</v>
-      </c>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C16" s="14" t="s">
@@ -18075,63 +16704,45 @@
       <c r="D16" s="16">
         <v>1</v>
       </c>
-      <c r="E16" s="20">
-        <v>0.85</v>
-      </c>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C17" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="16">
         <v>1</v>
       </c>
-      <c r="E17" s="20">
-        <v>0.85</v>
-      </c>
     </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C18" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
       </c>
-      <c r="E18" s="20">
-        <v>0.85</v>
-      </c>
     </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C19" s="14" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="16">
         <v>1</v>
       </c>
-      <c r="E19" s="20">
-        <v>0.85</v>
-      </c>
     </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" s="14" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="16">
         <v>1</v>
       </c>
-      <c r="E20" s="20">
-        <v>0.85</v>
-      </c>
     </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C21" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="16">
         <v>12</v>
-      </c>
-      <c r="E21" s="20">
-        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -18168,11 +16779,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="2:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>

--- a/src/lib/template/achievements-template.xlsx
+++ b/src/lib/template/achievements-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\TOHO(Fajar)\KCF\MC Monitoring System\kcf-mc-monitoring\src\lib\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6A5562-ED9B-4105-9090-0FC019AC20A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC60918-280F-4841-ADD5-57CEB41F0716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{370BB547-A0D3-4CB2-B344-9D3804543135}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -338,13 +338,13 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -890,6 +890,9 @@
       <c:pivotFmt>
         <c:idx val="3"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -1437,6 +1440,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2025,6 +2031,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2623,6 +2632,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -3215,6 +3227,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -3807,6 +3822,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4399,6 +4417,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4997,6 +5018,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -5595,6 +5619,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -6187,6 +6214,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -12789,1911 +12819,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1099930-AA0D-42B1-B26F-6D33ECEE56A5}" name="PivotTable21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="B50:C53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="7" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6D0FF5-F6F2-4E98-A793-3425B75F1FFE}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="EM4:EO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32494390-7516-4808-9564-94C6298A0B64}" name="PivotTable25" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="B70:C73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="0" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="18">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1">
-            <x v="2"/>
-          </reference>
-          <reference field="1" count="0" selected="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="17">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="7">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBEFD717-55D2-4077-BD74-B3665F7BCED5}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="DX4:DZ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A90CBD1C-EB98-462C-B899-A137F77093F8}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="CC4:CF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C678E28A-B4DB-4C7B-9C04-D16A9B79A051}" name="PivotTable20" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="B27:C30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="6" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CDF4683-225E-491F-BC53-BACA1AD4F4FB}" name="PivotTable23" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
-  <location ref="O27:P31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="4" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E9197E-66A0-4212-8D82-1C76DDF3FEE7}" name="PivotTable27" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25">
-  <location ref="B92:C95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="5" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="23" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983F6769-FF4F-45FA-A00D-3D6DA862D39D}" name="PivotTable28" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="FB4:FD7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="5" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A01F2CE9-B7B1-443F-AC32-A00886791260}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="CS4:CU7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3913DF35-F900-4B9E-A461-7854FE3E9E8A}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="C7:D21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="count" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="16">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="0" selected="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="15">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221D5A86-0FAF-4D4D-9C44-7BE90E19394D}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="AT4:AW7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F2800DD-182C-4C60-A59A-C1128AAB24B1}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
-  <location ref="B5:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" item="2" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <chartFormats count="7">
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="38" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="39" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="40" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A17830ED-8927-4755-8501-7DFC778792DA}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="DH4:DJ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04461318-0B3E-47A8-BB7B-19F4A3469DF7}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="AD4:AF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="13">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="10">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" item="0" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52385311-543D-48DA-9DB8-077801849FE9}" name="PivotTable24" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{52385311-543D-48DA-9DB8-077801849FE9}" name="PivotTable24" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
   <location ref="O5:P9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
@@ -14883,9 +13009,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{078CD331-B6DD-42D6-A2EA-38A1DC462D3C}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="BL4:BO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A90CBD1C-EB98-462C-B899-A137F77093F8}" name="PivotTable13" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="CC4:CF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisCol" showAll="0">
       <items count="13">
@@ -14953,17 +13079,17 @@
   </colFields>
   <colItems count="3">
     <i>
-      <x v="4"/>
+      <x v="5"/>
     </i>
     <i>
-      <x v="7"/>
+      <x v="8"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="3" item="2" hier="-1"/>
+    <pageField fld="3" item="3" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
@@ -14980,8 +13106,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E75A289-3383-4298-8FCC-8F5B4061FFF8}" name="PivotTable22" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E75A289-3383-4298-8FCC-8F5B4061FFF8}" name="PivotTable22" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
   <location ref="O49:P53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
@@ -15135,8 +13261,160 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B55F4480-DCD5-4360-899D-5EEB6809EDFC}" name="PivotTable26" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C678E28A-B4DB-4C7B-9C04-D16A9B79A051}" name="PivotTable20" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="B27:C30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="6" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B55F4480-DCD5-4360-899D-5EEB6809EDFC}" name="PivotTable26" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
   <location ref="O70:P73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" showAll="0">
@@ -15284,6 +13562,1758 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A17830ED-8927-4755-8501-7DFC778792DA}" name="PivotTable11" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="DH4:DJ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E6D0FF5-F6F2-4E98-A793-3425B75F1FFE}" name="PivotTable15" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="EM4:EO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="8" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CDF4683-225E-491F-BC53-BACA1AD4F4FB}" name="PivotTable23" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="O27:P31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="4" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04461318-0B3E-47A8-BB7B-19F4A3469DF7}" name="PivotTable8" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="AD4:AF7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32494390-7516-4808-9564-94C6298A0B64}" name="PivotTable25" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="B70:C73" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="0" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="16">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="7">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3913DF35-F900-4B9E-A461-7854FE3E9E8A}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="C7:D21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="18">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1099930-AA0D-42B1-B26F-6D33ECEE56A5}" name="PivotTable21" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+  <location ref="B50:C53" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="7" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{46E9197E-66A0-4212-8D82-1C76DDF3FEE7}" name="PivotTable27" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25">
+  <location ref="B92:C95" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="5" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221D5A86-0FAF-4D4D-9C44-7BE90E19394D}" name="PivotTable9" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="AT4:AW7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983F6769-FF4F-45FA-A00D-3D6DA862D39D}" name="PivotTable28" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="FB4:FD7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="5" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBEFD717-55D2-4077-BD74-B3665F7BCED5}" name="PivotTable14" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="DX4:DZ7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{078CD331-B6DD-42D6-A2EA-38A1DC462D3C}" name="PivotTable10" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="BL4:BO7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F2800DD-182C-4C60-A59A-C1128AAB24B1}" name="PivotTable17" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
+  <location ref="B5:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" item="2" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="RATE" fld="12" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="38" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="39" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="40" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A01F2CE9-B7B1-443F-AC32-A00886791260}" name="PivotTable12" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="CS4:CU7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of OPERATING RATE" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -15751,14 +15781,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:160" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
     </row>
     <row r="2" spans="2:160" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
@@ -16602,20 +16632,20 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C5" s="10" t="s">
@@ -16638,7 +16668,7 @@
         <v>43</v>
       </c>
       <c r="D8" s="16">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="3:12" x14ac:dyDescent="0.25">
@@ -16742,7 +16772,7 @@
         <v>14</v>
       </c>
       <c r="D21" s="16">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
